--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,6 +1024,2788 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114927695</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>531195</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6911195</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114927752</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79048</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>531203</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6911225</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114927739</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97455</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>531300</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6911231</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114927741</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79048</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>531312</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6911246</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114927689</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>531182</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6911193</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114927757</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>531167</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6911149</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114927694</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80376</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>531191</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6911199</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114927698</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96500</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>531229</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6911218</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114927699</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96500</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>531239</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6911215</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114927759</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96500</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>531160</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6911121</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114927691</v>
+      </c>
+      <c r="B15" t="n">
+        <v>74598</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>531190</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6911201</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114927754</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>531198</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6911212</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114927755</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>531175</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6911168</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114927738</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>531121</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6911098</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114927688</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78490</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>185</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>531200</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6911188</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114927744</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>531263</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6911273</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114927687</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74598</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>531201</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6911189</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114927758</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78196</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>531147</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6911132</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114927693</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>531192</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6911200</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114927690</v>
+      </c>
+      <c r="B24" t="n">
+        <v>74598</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>531183</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6911198</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114927743</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>531301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6911259</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>114927737</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>531105</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6911091</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114927756</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>531170</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6911167</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114927692</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>531192</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6911202</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>114927742</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>531305</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6911267</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>114927753</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>tovåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>531197</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6911219</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Filip Myllyaho, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>97567</v>
+        <v>98092</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,11 +2969,6 @@
       </c>
       <c r="E23" t="n">
         <v>219790</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,6 +2969,11 @@
       </c>
       <c r="E23" t="n">
         <v>219790</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 27326-2021 artfynd.xlsx
+++ b/artfynd/A 27326-2021 artfynd.xlsx
@@ -2955,7 +2955,7 @@
         <v>114927739</v>
       </c>
       <c r="B23" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
